--- a/src/ARK_NordicLCA_Housing_Timber_As-built_Archicad.xlsx
+++ b/src/ARK_NordicLCA_Housing_Timber_As-built_Archicad.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Check Counts'!$A$1:$AC$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Check Definitions'!$A$1:$G$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Methodology Notes'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Issues'!$A$1:$N$485</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Elements'!$A$1:$V$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Issues'!$A$1:$N$495</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Elements'!$A$1:$V$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1952,49 +1952,101 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.325</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr"/>
-      <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4287,34 +4339,86 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5792,7 +5896,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A populated PredefinedType that is not NOTDEFINED where the attribute exists.</t>
+          <t>A populated occurrence or assigned type-object PredefinedType that is not NOTDEFINED where the attribute exists. For IfcRoof, legacy ShapeType is also accepted.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6896,7 +7000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N485"/>
+  <dimension ref="A1:N495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16157,7 +16261,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M256" t="inlineStr"/>
@@ -16193,7 +16297,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M257" t="inlineStr"/>
@@ -16229,7 +16333,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M258" t="inlineStr"/>
@@ -16265,7 +16369,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M259" t="inlineStr"/>
@@ -16301,7 +16405,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M260" t="inlineStr"/>
@@ -16337,7 +16441,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M261" t="inlineStr"/>
@@ -16373,7 +16477,7 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M262" t="inlineStr"/>
@@ -16409,7 +16513,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M263" t="inlineStr"/>
@@ -16445,7 +16549,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M264" t="inlineStr"/>
@@ -16481,7 +16585,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M265" t="inlineStr"/>
@@ -16517,7 +16621,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M266" t="inlineStr"/>
@@ -16553,7 +16657,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M267" t="inlineStr"/>
@@ -16589,7 +16693,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M268" t="inlineStr"/>
@@ -16625,7 +16729,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M269" t="inlineStr"/>
@@ -16661,7 +16765,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M270" t="inlineStr"/>
@@ -16697,7 +16801,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M271" t="inlineStr"/>
@@ -16733,7 +16837,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>Unexpected IfcSlab.PredefinedType=NOTDEFINED; treated as 2.2</t>
+          <t>Unexpected IfcSlab.PredefinedType=None; treated as 2.2</t>
         </is>
       </c>
       <c r="M272" t="inlineStr"/>
@@ -16769,7 +16873,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSlab.PredefinedType)</t>
+          <t>Missing predefined type (IfcSlab.PredefinedType or assigned type PredefinedType)</t>
         </is>
       </c>
       <c r="M273" t="inlineStr"/>
@@ -16781,7 +16885,7 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -16793,7 +16897,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -16805,7 +16909,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M274" t="inlineStr"/>
@@ -16817,7 +16921,7 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -16829,7 +16933,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -16841,7 +16945,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M275" t="inlineStr"/>
@@ -16853,7 +16957,7 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -16865,7 +16969,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -16877,7 +16981,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M276" t="inlineStr"/>
@@ -16889,7 +16993,7 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -16901,7 +17005,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -16913,7 +17017,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M277" t="inlineStr"/>
@@ -16925,7 +17029,7 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -16937,7 +17041,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -16949,7 +17053,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M278" t="inlineStr"/>
@@ -16961,7 +17065,7 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -16973,7 +17077,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -16985,7 +17089,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M279" t="inlineStr"/>
@@ -16997,7 +17101,7 @@
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -17009,7 +17113,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -17021,7 +17125,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M280" t="inlineStr"/>
@@ -17033,7 +17137,7 @@
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E281" t="inlineStr"/>
@@ -17045,7 +17149,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -17057,7 +17161,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M281" t="inlineStr"/>
@@ -17069,7 +17173,7 @@
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E282" t="inlineStr"/>
@@ -17081,7 +17185,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -17093,7 +17197,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M282" t="inlineStr"/>
@@ -17105,7 +17209,7 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -17117,7 +17221,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -17129,7 +17233,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing roof type (IfcRoof.PredefinedType, assigned type PredefinedType, or IfcRoof.ShapeType)</t>
         </is>
       </c>
       <c r="M283" t="inlineStr"/>
@@ -17141,7 +17245,7 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -17177,7 +17281,7 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -17213,7 +17317,7 @@
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -17249,7 +17353,7 @@
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -17285,7 +17389,7 @@
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -17321,7 +17425,7 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -17357,7 +17461,7 @@
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -17429,7 +17533,7 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -17441,7 +17545,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -17465,7 +17569,7 @@
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -17477,7 +17581,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -17501,7 +17605,7 @@
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -17513,7 +17617,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -17537,7 +17641,7 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -17549,7 +17653,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -17573,7 +17677,7 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -17585,7 +17689,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -17609,7 +17713,7 @@
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -17621,7 +17725,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -17645,7 +17749,7 @@
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -17657,7 +17761,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -17669,7 +17773,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M298" t="inlineStr"/>
@@ -17681,7 +17785,7 @@
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -17693,7 +17797,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I299" t="inlineStr"/>
@@ -17705,7 +17809,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M299" t="inlineStr"/>
@@ -17717,7 +17821,7 @@
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E300" t="inlineStr"/>
@@ -17729,7 +17833,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I300" t="inlineStr"/>
@@ -17741,7 +17845,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M300" t="inlineStr"/>
@@ -17753,7 +17857,7 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -17765,7 +17869,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I301" t="inlineStr"/>
@@ -17777,7 +17881,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M301" t="inlineStr"/>
@@ -17789,7 +17893,7 @@
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -17801,7 +17905,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I302" t="inlineStr"/>
@@ -17813,7 +17917,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M302" t="inlineStr"/>
@@ -17825,7 +17929,7 @@
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -17837,7 +17941,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I303" t="inlineStr"/>
@@ -17849,7 +17953,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M303" t="inlineStr"/>
@@ -17861,7 +17965,7 @@
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -17873,7 +17977,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I304" t="inlineStr"/>
@@ -17885,7 +17989,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M304" t="inlineStr"/>
@@ -17897,7 +18001,7 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -17909,7 +18013,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I305" t="inlineStr"/>
@@ -17921,7 +18025,7 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M305" t="inlineStr"/>
@@ -17933,7 +18037,7 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E306" t="inlineStr"/>
@@ -17945,7 +18049,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I306" t="inlineStr"/>
@@ -17957,7 +18061,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M306" t="inlineStr"/>
@@ -17969,7 +18073,7 @@
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
@@ -17981,7 +18085,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="I307" t="inlineStr"/>
@@ -17993,7 +18097,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M307" t="inlineStr"/>
@@ -20237,7 +20341,7 @@
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
@@ -20249,7 +20353,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I370" t="inlineStr"/>
@@ -20261,7 +20365,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M370" t="inlineStr"/>
@@ -20273,7 +20377,7 @@
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
@@ -20285,7 +20389,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I371" t="inlineStr"/>
@@ -20297,7 +20401,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M371" t="inlineStr"/>
@@ -20309,7 +20413,7 @@
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
@@ -20321,7 +20425,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I372" t="inlineStr"/>
@@ -20333,7 +20437,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M372" t="inlineStr"/>
@@ -20345,7 +20449,7 @@
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
@@ -20357,7 +20461,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I373" t="inlineStr"/>
@@ -20369,7 +20473,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M373" t="inlineStr"/>
@@ -20381,7 +20485,7 @@
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
@@ -20393,7 +20497,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I374" t="inlineStr"/>
@@ -20405,7 +20509,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M374" t="inlineStr"/>
@@ -20417,7 +20521,7 @@
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
@@ -20429,7 +20533,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I375" t="inlineStr"/>
@@ -20441,7 +20545,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M375" t="inlineStr"/>
@@ -20453,7 +20557,7 @@
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
@@ -20465,7 +20569,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I376" t="inlineStr"/>
@@ -20477,7 +20581,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M376" t="inlineStr"/>
@@ -20489,7 +20593,7 @@
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
@@ -20501,7 +20605,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I377" t="inlineStr"/>
@@ -20513,7 +20617,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M377" t="inlineStr"/>
@@ -20525,7 +20629,7 @@
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E378" t="inlineStr"/>
@@ -20537,7 +20641,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I378" t="inlineStr"/>
@@ -20549,7 +20653,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M378" t="inlineStr"/>
@@ -20561,7 +20665,7 @@
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
@@ -20573,7 +20677,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="I379" t="inlineStr"/>
@@ -20585,7 +20689,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>Missing predefined type</t>
+          <t>Missing Pset_*Common.IsExternal for IfcDoor; external/internal classification is uncertain</t>
         </is>
       </c>
       <c r="M379" t="inlineStr"/>
@@ -22541,7 +22645,7 @@
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E434" t="inlineStr"/>
@@ -22565,7 +22669,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M434" t="inlineStr"/>
@@ -22577,7 +22681,7 @@
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E435" t="inlineStr"/>
@@ -22613,7 +22717,7 @@
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
@@ -22637,7 +22741,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M436" t="inlineStr"/>
@@ -22649,7 +22753,7 @@
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
@@ -22685,7 +22789,7 @@
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E438" t="inlineStr"/>
@@ -22709,7 +22813,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M438" t="inlineStr"/>
@@ -22721,7 +22825,7 @@
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
@@ -22757,7 +22861,7 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E440" t="inlineStr"/>
@@ -22781,7 +22885,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M440" t="inlineStr"/>
@@ -22793,7 +22897,7 @@
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
@@ -22829,7 +22933,7 @@
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
@@ -22853,7 +22957,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M442" t="inlineStr"/>
@@ -22865,7 +22969,7 @@
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
@@ -23763,29 +23867,33 @@
       <c r="A468" t="inlineStr"/>
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>IfcBuildingElementProxy</t>
+        </is>
+      </c>
       <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>element</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
         <is>
-          <t>Kitchen equipment is not exported in because no deterministic IFC category-membership signal has been found.</t>
+          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
         </is>
       </c>
       <c r="M468" t="inlineStr"/>
@@ -23795,29 +23903,33 @@
       <c r="A469" t="inlineStr"/>
       <c r="B469" t="inlineStr"/>
       <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>IfcBuildingElementProxy</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr"/>
       <c r="F469" t="inlineStr"/>
       <c r="G469" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>element</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I469" t="inlineStr"/>
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>Special equipment is not exported in the publication-facing pipeline because no deterministic IFC category-membership signal has been adopted.</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M469" t="inlineStr"/>
@@ -23827,29 +23939,33 @@
       <c r="A470" t="inlineStr"/>
       <c r="B470" t="inlineStr"/>
       <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>IfcBuildingElementProxy</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>element</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I470" t="inlineStr"/>
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>warning</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>Loose FF&amp;E is not exported in the publication-facing pipeline because no deterministic IFC category-membership signal has been adopted.</t>
+          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
         </is>
       </c>
       <c r="M470" t="inlineStr"/>
@@ -23861,7 +23977,7 @@
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E471" t="inlineStr"/>
@@ -23873,7 +23989,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I471" t="inlineStr"/>
@@ -23885,7 +24001,7 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M471" t="inlineStr"/>
@@ -23897,7 +24013,7 @@
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E472" t="inlineStr"/>
@@ -23909,7 +24025,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I472" t="inlineStr"/>
@@ -23921,7 +24037,7 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
         </is>
       </c>
       <c r="M472" t="inlineStr"/>
@@ -23933,7 +24049,7 @@
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E473" t="inlineStr"/>
@@ -23945,7 +24061,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I473" t="inlineStr"/>
@@ -23957,7 +24073,7 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M473" t="inlineStr"/>
@@ -23969,7 +24085,7 @@
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E474" t="inlineStr"/>
@@ -23981,7 +24097,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I474" t="inlineStr"/>
@@ -23993,7 +24109,7 @@
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
         </is>
       </c>
       <c r="M474" t="inlineStr"/>
@@ -24005,7 +24121,7 @@
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E475" t="inlineStr"/>
@@ -24017,7 +24133,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I475" t="inlineStr"/>
@@ -24029,7 +24145,7 @@
       </c>
       <c r="L475" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M475" t="inlineStr"/>
@@ -24041,7 +24157,7 @@
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E476" t="inlineStr"/>
@@ -24053,7 +24169,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I476" t="inlineStr"/>
@@ -24065,7 +24181,7 @@
       </c>
       <c r="L476" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Element is IfcBuildingElementProxy; FF&amp;E classification is uncertain (consider IfcFurniture/IfcEquipmentElement + classification)</t>
         </is>
       </c>
       <c r="M476" t="inlineStr"/>
@@ -24077,7 +24193,7 @@
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="E477" t="inlineStr"/>
@@ -24089,7 +24205,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="I477" t="inlineStr"/>
@@ -24101,7 +24217,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Missing predefined type</t>
         </is>
       </c>
       <c r="M477" t="inlineStr"/>
@@ -24111,33 +24227,29 @@
       <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>IfcSanitaryTerminal</t>
-        </is>
-      </c>
+      <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
       <c r="G478" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>category</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I478" t="inlineStr"/>
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Kitchen equipment is not exported in because no deterministic IFC category-membership signal has been found.</t>
         </is>
       </c>
       <c r="M478" t="inlineStr"/>
@@ -24147,33 +24259,29 @@
       <c r="A479" t="inlineStr"/>
       <c r="B479" t="inlineStr"/>
       <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>IfcSanitaryTerminal</t>
-        </is>
-      </c>
+      <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr"/>
       <c r="F479" t="inlineStr"/>
       <c r="G479" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>category</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="L479" t="inlineStr">
         <is>
-          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+          <t>Special equipment is not exported in the pipeline because no deterministic IFC category-membership signal has been adopted.</t>
         </is>
       </c>
       <c r="M479" t="inlineStr"/>
@@ -24183,33 +24291,29 @@
       <c r="A480" t="inlineStr"/>
       <c r="B480" t="inlineStr"/>
       <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>IfcDistributionSystem</t>
-        </is>
-      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>category</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>5.1.2</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="I480" t="inlineStr"/>
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>info</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
         <is>
-          <t>No cold water system found (expected IfcDistributionSystem.PredefinedType=DOMESTICCOLDWATER)</t>
+          <t>Loose FF&amp;E is not exported in the pipeline because no deterministic IFC category-membership signal has been adopted.</t>
         </is>
       </c>
       <c r="M480" t="inlineStr"/>
@@ -24221,7 +24325,7 @@
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>IfcDistributionSystem</t>
+          <t>IfcSanitaryTerminal</t>
         </is>
       </c>
       <c r="E481" t="inlineStr"/>
@@ -24233,7 +24337,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>5.2.1</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="I481" t="inlineStr"/>
@@ -24245,7 +24349,7 @@
       </c>
       <c r="L481" t="inlineStr">
         <is>
-          <t>No heating/DHW system found (expected IfcDistributionSystem.PredefinedType=HEATING or DOMESTICHOTWATER)</t>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
         </is>
       </c>
       <c r="M481" t="inlineStr"/>
@@ -24257,7 +24361,7 @@
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>IfcDistributionSystem</t>
+          <t>IfcSanitaryTerminal</t>
         </is>
       </c>
       <c r="E482" t="inlineStr"/>
@@ -24269,7 +24373,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>5.2.2</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
@@ -24281,7 +24385,7 @@
       </c>
       <c r="L482" t="inlineStr">
         <is>
-          <t>No cooling system found (expected explicit IfcDistributionSystem cooling PredefinedType)</t>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
         </is>
       </c>
       <c r="M482" t="inlineStr"/>
@@ -24291,7 +24395,11 @@
       <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr"/>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
@@ -24301,7 +24409,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>5.3.1</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="I483" t="inlineStr"/>
@@ -24313,7 +24421,7 @@
       </c>
       <c r="L483" t="inlineStr">
         <is>
-          <t>No lighting fixtures found (expected IfcLightFixture)</t>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
         </is>
       </c>
       <c r="M483" t="inlineStr"/>
@@ -24323,7 +24431,11 @@
       <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr"/>
       <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
@@ -24333,7 +24445,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="I484" t="inlineStr"/>
@@ -24345,7 +24457,7 @@
       </c>
       <c r="L484" t="inlineStr">
         <is>
-          <t>No deterministic 5.5 service elements found (fire terminals, distribution systems, transport elements, waste terminals/interceptors)</t>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
         </is>
       </c>
       <c r="M484" t="inlineStr"/>
@@ -24355,7 +24467,11 @@
       <c r="A485" t="inlineStr"/>
       <c r="B485" t="inlineStr"/>
       <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr"/>
       <c r="G485" t="inlineStr">
@@ -24365,7 +24481,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="I485" t="inlineStr"/>
@@ -24377,14 +24493,362 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>Excluded generic proxy elements without deterministic category routing: 17</t>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
         </is>
       </c>
       <c r="M485" t="inlineStr"/>
       <c r="N485" t="inlineStr"/>
     </row>
+    <row r="486">
+      <c r="A486" t="inlineStr"/>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr"/>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr"/>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr"/>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr"/>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Missing predefined type (IfcSanitaryTerminal.PredefinedType)</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr"/>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>IfcDistributionSystem</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>5.1.2</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>No cold water system found (expected IfcDistributionSystem.PredefinedType=DOMESTICCOLDWATER)</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr"/>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>IfcDistributionSystem</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>5.2.1</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>No heating/DHW system found (expected IfcDistributionSystem.PredefinedType=HEATING or DOMESTICHOTWATER)</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr"/>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>IfcDistributionSystem</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>5.2.2</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>No cooling system found (expected explicit IfcDistributionSystem cooling PredefinedType)</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr"/>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr"/>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>5.3.1</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>No lighting fixtures found (expected IfcLightFixture)</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr"/>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr"/>
+      <c r="E494" t="inlineStr"/>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>No deterministic 5.5 service elements found (fire terminals, distribution systems, transport elements, waste terminals/interceptors)</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr"/>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr"/>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Excluded generic proxy elements without deterministic category routing: 17</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N485"/>
+  <autoFilter ref="A1:N495"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -24395,7 +24859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27879,24 +28343,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>3wWyxgPUT5N9BcQl4RpjcR</t>
+          <t>2YqQyiRFnCCfGOvXZwANFG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -27908,15 +28372,15 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Betoni</t>
+          <t>YP-3.AUTOT Ranka - verhousrakenteet Tuulensuoja Eriste, villa Rakennuslevy Palosuojaus</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>2.002</v>
+        <v>11.435</v>
       </c>
       <c r="M53" t="n">
-        <v>13.694</v>
+        <v>7.675</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -27945,44 +28409,44 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>23213</t>
+          <t>27430</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3xOnqpcHD20AWXaaW2LnRQ</t>
+          <t>1P9nwcP4kdqcpwv6_pa5Tm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>IfcStair</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Puuverhous</t>
+          <t>KA-1 Puu</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>4.208</v>
+        <v>1.402</v>
       </c>
       <c r="M54" t="n">
-        <v>43.036</v>
+        <v>14.015</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -28011,44 +28475,44 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2pUeGKn_107hdiP_oRqnjv</t>
+          <t>0HJ35Uo$nAI82bVwzBBJqX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Metalli Alumiini</t>
+          <t>VK-2 Metallipinnoite Puu</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>0.219</v>
+        <v>0.927</v>
       </c>
       <c r="M55" t="n">
-        <v>9.957000000000001</v>
+        <v>11.037</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -28077,44 +28541,44 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>69811</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>3XiS$ktYHDvBBSPoxFv5$v</t>
+          <t>23FscXZiL25u6t_bNw9cPZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IfcRailing</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Metalli</t>
+          <t>YP-4.Parvekkeet Kalvo Vaneri Ranka - verhousrakenteet Puu CLT Ranka Palosuojaus</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>0.5639999999999999</v>
+        <v>8.695</v>
       </c>
       <c r="M56" t="n">
-        <v>70.98399999999999</v>
+        <v>13.628</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -28143,44 +28607,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>35851</t>
+          <t>70585</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>33tOBplkb5bvQlA8dttZnY</t>
+          <t>2vOZijX_P6xwmwIkUNr7ln</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>IfcCurtainWall</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Lasi Alumiini</t>
+          <t>VK-1 Metallipinnoite Puu Ranka</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>1.273</v>
+        <v>54.679</v>
       </c>
       <c r="M57" t="n">
-        <v>163.233</v>
+        <v>142.558</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -28209,29 +28673,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>73426</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3Dkdn4BPDAvxhqswfutrnf</t>
+          <t>0G7e79QznBywVu95UGqaak</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>IfcWindow</t>
+          <t>IfcRoof</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -28239,10 +28703,10 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>4.587</v>
+        <v>2.824</v>
       </c>
       <c r="M58" t="n">
-        <v>60.618</v>
+        <v>8.897</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -28271,24 +28735,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>70947</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0G3xVj3yT5aBS3sZJ4n5_y</t>
+          <t>3wWyxgPUT5N9BcQl4RpjcR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>IfcWindow</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -28298,13 +28762,17 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Betoni</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>10.279</v>
+        <v>2.002</v>
       </c>
       <c r="M59" t="n">
-        <v>0.32</v>
+        <v>13.694</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -28314,7 +28782,7 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
@@ -28333,40 +28801,44 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>23213</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04tZ8zTjnCjO2YjNVFtyLY</t>
+          <t>3xOnqpcHD20AWXaaW2LnRQ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcStair</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Puuverhous</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>7.014</v>
+        <v>4.208</v>
       </c>
       <c r="M60" t="n">
-        <v>93.476</v>
+        <v>43.036</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -28376,7 +28848,7 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="b">
         <v>0</v>
@@ -28395,40 +28867,44 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>70090</t>
+          <t>24270</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1Zs796xIX0HPEQqGRxdXFD</t>
+          <t>2pUeGKn_107hdiP_oRqnjv</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>IfcDoor</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Metalli Alumiini</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>10.279</v>
+        <v>0.219</v>
       </c>
       <c r="M61" t="n">
-        <v>0.32</v>
+        <v>9.957000000000001</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -28438,7 +28914,7 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
       <c r="S61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="b">
         <v>0</v>
@@ -28457,44 +28933,44 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>23349</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1x$2CULur3BRvYxlVYi7kp</t>
+          <t>3XiS$ktYHDvBBSPoxFv5$v</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>IfcCovering</t>
+          <t>IfcRailing</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Alakattopinta ja alakatto-ontelo</t>
+          <t>Metalli</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>9.83</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>9.824</v>
+        <v>70.98399999999999</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -28523,44 +28999,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>37665</t>
+          <t>35851</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14HO7rwYvFXwPLJL3Yz9si</t>
+          <t>33tOBplkb5bvQlA8dttZnY</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IfcCovering</t>
+          <t>IfcCurtainWall</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>AK-2 Ranka - verhousrakenteet Puuverhous</t>
+          <t>Lasi Alumiini</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>1.811</v>
+        <v>1.273</v>
       </c>
       <c r="M63" t="n">
-        <v>20.917</v>
+        <v>163.233</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -28589,44 +29065,40 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>16562</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1mc5_YZI12KPgezyXcsQvS</t>
+          <t>3Dkdn4BPDAvxhqswfutrnf</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IfcCovering</t>
+          <t>IfcWindow</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>AK-1 Ranka - verhousrakenteet Kipsilevy</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>5.504</v>
+        <v>4.587</v>
       </c>
       <c r="M64" t="n">
-        <v>80.84399999999999</v>
+        <v>60.618</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -28636,7 +29108,7 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="b">
         <v>0</v>
@@ -28655,44 +29127,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1K37eP1a92SfDGHBnEfn2A</t>
+          <t>0G3xVj3yT5aBS3sZJ4n5_y</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>IfcCovering</t>
+          <t>IfcWindow</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>AK-otsa Ranka - verhousrakenteet Kipsilevy</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>0.207</v>
+        <v>10.279</v>
       </c>
       <c r="M65" t="n">
-        <v>0.103</v>
+        <v>0.32</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -28702,7 +29170,7 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="b">
         <v>0</v>
@@ -28721,29 +29189,29 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2GUG_QEo5EnggyvHtmCCfu</t>
+          <t>04tZ8zTjnCjO2YjNVFtyLY</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
@@ -28751,10 +29219,10 @@
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>52.907</v>
+        <v>7.014</v>
       </c>
       <c r="M66" t="n">
-        <v>184.178</v>
+        <v>93.476</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -28783,44 +29251,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>38253</t>
+          <t>70090</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0yWdyjiKH0ZwET2lsIrtl8</t>
+          <t>1Zs796xIX0HPEQqGRxdXFD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>IfcFurniture</t>
+          <t>IfcDoor</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Yleinen tilavaraus</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>14.451</v>
+        <v>10.279</v>
       </c>
       <c r="M67" t="n">
-        <v>48.814</v>
+        <v>0.32</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -28830,7 +29294,7 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="b">
         <v>0</v>
@@ -28849,44 +29313,44 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>23349</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>3HbjQIGP11quR0rIGXyyDO</t>
+          <t>1x$2CULur3BRvYxlVYi7kp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcCovering</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Yleinen tilavaraus</t>
+          <t>Alakattopinta ja alakatto-ontelo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>6</v>
+        <v>9.83</v>
       </c>
       <c r="M68" t="n">
-        <v>11</v>
+        <v>9.824</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -28915,40 +29379,44 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>37665</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2iIJISwlH0H93V5mtXm535</t>
+          <t>14HO7rwYvFXwPLJL3Yz9si</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>IfcBuildingElementProxy</t>
+          <t>IfcCovering</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>AK-2 Ranka - verhousrakenteet Puuverhous</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
-        <v>0.121</v>
+        <v>1.811</v>
       </c>
       <c r="M69" t="n">
-        <v>47.487</v>
+        <v>20.917</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -28958,7 +29426,7 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69" t="b">
         <v>0</v>
@@ -28977,40 +29445,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>27772</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>28ZVPCm8LDUOm9lhetdHAn</t>
+          <t>1mc5_YZI12KPgezyXcsQvS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcCovering</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>AK-1 Ranka - verhousrakenteet Kipsilevy</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
-        <v>71.59999999999999</v>
+        <v>5.504</v>
       </c>
       <c r="M70" t="n">
-        <v>5.329</v>
+        <v>80.84399999999999</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -29020,7 +29492,7 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" t="b">
         <v>0</v>
@@ -29039,24 +29511,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>52179</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0HC5$t0wX4tAN968IanaZ4</t>
+          <t>1K37eP1a92SfDGHBnEfn2A</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcCovering</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -29066,13 +29538,17 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>AK-otsa Ranka - verhousrakenteet Kipsilevy</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
-        <v>0.008</v>
+        <v>0.207</v>
       </c>
       <c r="M71" t="n">
-        <v>0.613</v>
+        <v>0.103</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -29082,7 +29558,7 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="b">
         <v>0</v>
@@ -29101,29 +29577,29 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>35935</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3s1nOLOB527wLmpI9RXhHm</t>
+          <t>2GUG_QEo5EnggyvHtmCCfu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>IfcSanitaryTerminal</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
@@ -29131,10 +29607,10 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
-        <v>19.63</v>
+        <v>52.907</v>
       </c>
       <c r="M72" t="n">
-        <v>1.546</v>
+        <v>184.178</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -29163,40 +29639,44 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5.1.3.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>38253</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1ZjivcYzT20AbGoeMadLcR</t>
+          <t>0yWdyjiKH0ZwET2lsIrtl8</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>IfcWasteTerminal</t>
+          <t>IfcFurniture</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Yleinen tilavaraus</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
-        <v>0.006</v>
+        <v>14.451</v>
       </c>
       <c r="M73" t="n">
-        <v>3.452</v>
+        <v>48.814</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -29206,7 +29686,7 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73" t="b">
         <v>0</v>
@@ -29225,24 +29705,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5.4.1.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>73578</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0l3a9$1c5BK8aPJBPXh$gY</t>
+          <t>3HbjQIGP11quR0rIGXyyDO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>IfcSolarDevice</t>
+          <t>IfcBuildingElementProxy</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -29252,13 +29732,17 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Yleinen tilavaraus</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>25.684</v>
+        <v>6</v>
       </c>
       <c r="M74" t="n">
-        <v>4.359</v>
+        <v>11</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -29268,24 +29752,396 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="b">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>17113</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2iIJISwlH0H93V5mtXm535</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>IfcBuildingElementProxy</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>16</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M75" t="n">
+        <v>47.487</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="b">
         <v>1</v>
       </c>
-      <c r="T74" t="b">
-        <v>0</v>
-      </c>
-      <c r="U74" t="inlineStr">
+      <c r="T75" t="b">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>27772</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>28ZVPCm8LDUOm9lhetdHAn</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>13</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="M76" t="n">
+        <v>5.329</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="b">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>28148</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0HC5$t0wX4tAN968IanaZ4</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="b">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5.1.1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>38847</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>3s1nOLOB527wLmpI9RXhHm</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>IfcSanitaryTerminal</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>9</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="b">
+        <v>0</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5.1.3.1</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19308</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1ZjivcYzT20AbGoeMadLcR</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>IfcWasteTerminal</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.452</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="b">
+        <v>0</v>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>5.4.1.1</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>73578</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0l3a9$1c5BK8aPJBPXh$gY</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>IfcSolarDevice</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>25.684</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4.359</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="b">
+        <v>0</v>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V74"/>
+  <autoFilter ref="A1:V80"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>